--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-01-2026.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£11.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>£46.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£51.7</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£89.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£70.18</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
